--- a/artfynd/A 22978-2023 artfynd.xlsx
+++ b/artfynd/A 22978-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22978-2023 artfynd.xlsx
+++ b/artfynd/A 22978-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>105299898</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564406.1106809843</v>
+        <v>564406</v>
       </c>
       <c r="R2" t="n">
-        <v>6854086.131583135</v>
+        <v>6854087</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>105299895</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564396.1888055068</v>
+        <v>564396</v>
       </c>
       <c r="R3" t="n">
-        <v>6854084.999461411</v>
+        <v>6854085</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105299896</v>
+        <v>105299904</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564395.2421720544</v>
+        <v>564460</v>
       </c>
       <c r="R4" t="n">
-        <v>6854084.981661998</v>
+        <v>6854085</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,21 +947,11 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Hård, rötad granlåga.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,50 +981,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105299901</v>
+        <v>105299892</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullbergets bergtäkt, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564415.8636568876</v>
+        <v>564365</v>
       </c>
       <c r="R5" t="n">
-        <v>6854096.243232443</v>
+        <v>6854112</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1094,19 +1053,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105299892</v>
+        <v>105299894</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1112,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564364.8902882094</v>
+        <v>564361</v>
       </c>
       <c r="R6" t="n">
-        <v>6854112.777368543</v>
+        <v>6854114</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,19 +1154,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,15 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105299902</v>
+        <v>105299897</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1213,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564448.2002784369</v>
+        <v>564399</v>
       </c>
       <c r="R7" t="n">
-        <v>6854088.814467138</v>
+        <v>6854086</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,24 +1255,14 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bland 80-åriga granar och tallar i flack nordsluttning.</t>
+          <t>Massa plantor på liten yta i nordsluttning i barrskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,15 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105299897</v>
+        <v>105299899</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1319,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564399.0287058434</v>
+        <v>564405</v>
       </c>
       <c r="R8" t="n">
-        <v>6854085.052861218</v>
+        <v>6854089</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,24 +1361,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Massa plantor på liten yta i nordsluttning i barrskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,50 +1390,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105299904</v>
+        <v>105299900</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullbergets bergtäkt, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564460.1132411398</v>
+        <v>564404</v>
       </c>
       <c r="R9" t="n">
-        <v>6854084.78370844</v>
+        <v>6854084</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,21 +1462,11 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1587,11 +1475,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Hård, rötad granlåga.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1608,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105299899</v>
+        <v>105299902</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1521,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564405.1107219465</v>
+        <v>564448</v>
       </c>
       <c r="R10" t="n">
-        <v>6854088.949415697</v>
+        <v>6854088</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,19 +1563,14 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bland 80-åriga granar och tallar i flack nordsluttning.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,15 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105299900</v>
+        <v>105299905</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1627,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564404.2529647558</v>
+        <v>564472</v>
       </c>
       <c r="R11" t="n">
-        <v>6854084.205554627</v>
+        <v>6854072</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1801,19 +1669,14 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid basen av en björk i 50-årig granskog. Nyligen gallrat nära intill.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,12 +1706,7 @@
         <v>105299891</v>
       </c>
       <c r="B12" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564457.0064955001</v>
+        <v>564457</v>
       </c>
       <c r="R12" t="n">
-        <v>6854098.908415047</v>
+        <v>6854098</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,19 +1771,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,54 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105299894</v>
+        <v>105299896</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kullbergets bergtäkt, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564361.0860221009</v>
+        <v>564396</v>
       </c>
       <c r="R13" t="n">
-        <v>6854113.651411353</v>
+        <v>6854085</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2029,19 +1868,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,6 +1894,200 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105299901</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kullbergets bergtäkt, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564416</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6854097</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105299903</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kullbergets bergtäkt, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>564466</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6854093</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22978-2023 artfynd.xlsx
+++ b/artfynd/A 22978-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299895</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299897</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299899</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299900</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299902</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299905</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299891</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299896</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299901</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,8 +2158,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105299903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>